--- a/reports/Analisis_Metas_Calzapato.xlsx
+++ b/reports/Analisis_Metas_Calzapato.xlsx
@@ -573,7 +573,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>➡️ Estable</t>
+          <t>⚠️ Sin datos recientes</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>➡️ Estable</t>
+          <t>⚠️ Sin datos recientes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1624,7 +1624,7 @@
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="36" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>➡️ Estable</t>
+          <t>⚠️ Sin datos recientes</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>➡️ Estable</t>
+          <t>⚠️ Sin datos recientes</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>➡️ Estable</t>
+          <t>⚠️ Sin datos recientes</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>➡️ Estable</t>
+          <t>⚠️ Sin datos recientes</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>➡️ Estable</t>
+          <t>⚠️ Sin datos recientes</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
